--- a/docs/Travel Reporting Requirements.xlsx
+++ b/docs/Travel Reporting Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hollywoodbets365-my.sharepoint.com/personal/tyran_hollywoodbets_net/Documents/Desktop/Work/Projects/Travel Report_Ian/Report Requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NMukhuba\Downloads\Projects\GHEtoTravel\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="614" documentId="11_F25DC773A252ABDACC104821791A54C85BDE58EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F47F554-C8EF-4E51-AD38-06E346097FD5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7749E5DE-ED43-4A20-AAD2-333E352D0EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report Columns Required" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="68">
   <si>
     <t>Date Dimensions</t>
   </si>
@@ -145,15 +145,6 @@
     <t>Billing Company</t>
   </si>
   <si>
-    <t>Flight</t>
-  </si>
-  <si>
-    <t>Hotel</t>
-  </si>
-  <si>
-    <t>Car Hire</t>
-  </si>
-  <si>
     <t>Internal</t>
   </si>
   <si>
@@ -166,187 +157,10 @@
     <t>Return</t>
   </si>
   <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Marketing</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
     <t>Traveller</t>
   </si>
   <si>
     <t>Amount (R)</t>
-  </si>
-  <si>
-    <t>TRV-2024-0001</t>
-  </si>
-  <si>
-    <t>John Smith</t>
-  </si>
-  <si>
-    <t>Hollywoodbets</t>
-  </si>
-  <si>
-    <t>Marketing Manager</t>
-  </si>
-  <si>
-    <t>Domestic</t>
-  </si>
-  <si>
-    <t>Conference</t>
-  </si>
-  <si>
-    <t>JNB</t>
-  </si>
-  <si>
-    <t>CPT</t>
-  </si>
-  <si>
-    <t>M. Naidoo</t>
-  </si>
-  <si>
-    <t>TRV-2024-0002</t>
-  </si>
-  <si>
-    <t>Sarah Naicker</t>
-  </si>
-  <si>
-    <t>Purple Team</t>
-  </si>
-  <si>
-    <t>Operations Lead</t>
-  </si>
-  <si>
-    <t>Site Visit</t>
-  </si>
-  <si>
-    <t>DUR</t>
-  </si>
-  <si>
-    <t>S. Govender</t>
-  </si>
-  <si>
-    <t>TRV-2024-0003</t>
-  </si>
-  <si>
-    <t>Ahmed Khan</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>IT Analyst</t>
-  </si>
-  <si>
-    <t>Training</t>
-  </si>
-  <si>
-    <t>TRV-2024-0004</t>
-  </si>
-  <si>
-    <t>Lerato Mokoena</t>
-  </si>
-  <si>
-    <t>Gold Circle</t>
-  </si>
-  <si>
-    <t>Retail</t>
-  </si>
-  <si>
-    <t>Retail Manager</t>
-  </si>
-  <si>
-    <t>Meeting</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>T. Mokoena</t>
-  </si>
-  <si>
-    <t>TRV-2024-0005</t>
-  </si>
-  <si>
-    <t>Peter Jacob</t>
-  </si>
-  <si>
-    <t>Operations Officer</t>
-  </si>
-  <si>
-    <t>CTG</t>
-  </si>
-  <si>
-    <t>TRV-2024-0006</t>
-  </si>
-  <si>
-    <t>Nicole Pillay</t>
-  </si>
-  <si>
-    <t>Brand Specialist</t>
-  </si>
-  <si>
-    <t>International</t>
-  </si>
-  <si>
-    <t>LON</t>
-  </si>
-  <si>
-    <t>TRV-2024-0007</t>
-  </si>
-  <si>
-    <t>Thabo Dlamini</t>
-  </si>
-  <si>
-    <t>Systems Analyst</t>
-  </si>
-  <si>
-    <t>Project Work</t>
-  </si>
-  <si>
-    <t>BFN</t>
-  </si>
-  <si>
-    <t>TRV-2024-0008</t>
-  </si>
-  <si>
-    <t>Priya Reddy</t>
-  </si>
-  <si>
-    <t>Financial Analyst</t>
-  </si>
-  <si>
-    <t>DXB</t>
-  </si>
-  <si>
-    <t>TRV-2024-0009</t>
-  </si>
-  <si>
-    <t>Michael Botha</t>
-  </si>
-  <si>
-    <t>Compliance</t>
-  </si>
-  <si>
-    <t>Compliance Officer</t>
-  </si>
-  <si>
-    <t>Audit</t>
-  </si>
-  <si>
-    <t>PMB</t>
-  </si>
-  <si>
-    <t>TRV-2024-0010</t>
-  </si>
-  <si>
-    <t>Jessica Govender</t>
-  </si>
-  <si>
-    <t>Marketing Executive</t>
   </si>
   <si>
     <t>Text</t>
@@ -439,7 +253,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -679,7 +493,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -762,7 +576,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -835,7 +649,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="20" formatCode="dd\-mmm\-yy"/>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
     </dxf>
     <dxf>
       <font>
@@ -1061,7 +875,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="20" formatCode="dd\-mmm\-yy"/>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
     </dxf>
     <dxf>
       <font>
@@ -1076,7 +890,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="20" formatCode="dd\-mmm\-yy"/>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
     </dxf>
     <dxf>
       <font>
@@ -1091,7 +905,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="20" formatCode="dd\-mmm\-yy"/>
+      <numFmt numFmtId="165" formatCode="dd\-mmm\-yy"/>
     </dxf>
     <dxf>
       <font>
@@ -1157,8 +971,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83D50E1F-1F2C-4418-9EC8-0B7F11FC9345}" name="Table1" displayName="Table1" ref="A1:U11" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="A1:U11" xr:uid="{83D50E1F-1F2C-4418-9EC8-0B7F11FC9345}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{83D50E1F-1F2C-4418-9EC8-0B7F11FC9345}" name="Table1" displayName="Table1" ref="A1:U2" insertRow="1" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A1:U2" xr:uid="{83D50E1F-1F2C-4418-9EC8-0B7F11FC9345}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{1684FA1E-4093-47C7-B7B9-5E2F0DE904E5}" name="Date Booked" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{3FA09E0C-A867-4C2F-8816-33AF77A9C491}" name="Date Of Departure" dataDxfId="19"/>
@@ -1476,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="G1" s="31"/>
     </row>
@@ -1545,10 +1359,10 @@
         <v>9</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="F5" s="32"/>
       <c r="G5" s="33"/>
@@ -1564,10 +1378,10 @@
         <v>9</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="F6" s="34"/>
       <c r="G6" s="35"/>
@@ -1586,7 +1400,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1597,13 +1411,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1620,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1631,7 +1445,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>6</v>
@@ -1649,10 +1463,10 @@
         <v>20</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1660,7 +1474,7 @@
         <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>20</v>
@@ -1678,7 +1492,7 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>6</v>
@@ -1696,13 +1510,13 @@
         <v>20</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>1</v>
@@ -1714,7 +1528,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1722,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>20</v>
@@ -1737,13 +1551,13 @@
         <v>0</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>22</v>
@@ -1774,7 +1588,7 @@
         <v>24</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>6</v>
@@ -1795,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1806,13 +1620,13 @@
         <v>26</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>6</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1823,7 +1637,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>6</v>
@@ -1844,7 +1658,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1855,7 +1669,7 @@
         <v>29</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>6</v>
@@ -1873,10 +1687,10 @@
         <v>5</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>115</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1899,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1910,7 +1724,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>6</v>
@@ -1956,12 +1770,12 @@
         <v>16</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
-        <v>124</v>
+        <v>62</v>
       </c>
       <c r="B2" s="11" t="b">
         <v>0</v>
@@ -1969,7 +1783,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="27" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="B3" s="11" t="b">
         <v>0</v>
@@ -1977,7 +1791,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="27" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="B4" s="11" t="b">
         <v>0</v>
@@ -1985,7 +1799,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="27" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="B5" s="11" t="b">
         <v>0</v>
@@ -1993,7 +1807,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="27" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="B6" s="11" t="b">
         <v>0</v>
@@ -2001,7 +1815,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="27" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="B7" s="11" t="b">
         <v>0</v>
@@ -2009,7 +1823,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="B8" s="11" t="b">
         <v>0</v>
@@ -2017,7 +1831,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="B9" s="11" t="b">
         <v>0</v>
@@ -2025,7 +1839,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="B10" s="11" t="b">
         <v>0</v>
@@ -2033,7 +1847,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="B11" s="11" t="b">
         <v>0</v>
@@ -2044,12 +1858,12 @@
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14" s="11" t="b">
         <v>0</v>
@@ -2057,7 +1871,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B15" s="11" t="b">
         <v>0</v>
@@ -2065,15 +1879,15 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="27" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B18" s="11" t="b">
         <v>0</v>
@@ -2081,7 +1895,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B19" s="11" t="b">
         <v>0</v>
@@ -2099,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0CD107-46F8-4009-9584-7CE3E38FE697}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -2146,7 +1960,7 @@
         <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>16</v>
@@ -2161,10 +1975,10 @@
         <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="M1" s="23" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>21</v>
@@ -2185,671 +1999,17 @@
         <v>30</v>
       </c>
       <c r="T1" s="26" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
-        <v>45413</v>
-      </c>
-      <c r="B2" s="13">
-        <v>45417</v>
-      </c>
-      <c r="C2" s="13">
-        <v>45420</v>
-      </c>
-      <c r="D2" s="1">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S2" s="13">
-        <v>45413</v>
-      </c>
-      <c r="T2" s="26">
-        <v>6450</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="13">
-        <v>45413</v>
-      </c>
-      <c r="B3" s="13">
-        <v>45418</v>
-      </c>
-      <c r="C3" s="13">
-        <v>45418</v>
-      </c>
-      <c r="D3" s="1">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S3" s="13">
-        <v>45413</v>
-      </c>
-      <c r="T3" s="26">
-        <v>1250</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="13">
-        <v>45414</v>
-      </c>
-      <c r="B4" s="13">
-        <v>45422</v>
-      </c>
-      <c r="C4" s="13">
-        <v>45424</v>
-      </c>
-      <c r="D4" s="1">
-        <v>19</v>
-      </c>
-      <c r="E4" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>3</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S4" s="13">
-        <v>45414</v>
-      </c>
-      <c r="T4" s="26">
-        <v>3800</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
-        <v>45415</v>
-      </c>
-      <c r="B5" s="13">
-        <v>45424</v>
-      </c>
-      <c r="C5" s="13">
-        <v>45427</v>
-      </c>
-      <c r="D5" s="1">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>4</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S5" s="13">
-        <v>45415</v>
-      </c>
-      <c r="T5" s="26">
-        <v>4780</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
-        <v>45415</v>
-      </c>
-      <c r="B6" s="13">
-        <v>45426</v>
-      </c>
-      <c r="C6" s="13">
-        <v>45426</v>
-      </c>
-      <c r="D6" s="1">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S6" s="13">
-        <v>45415</v>
-      </c>
-      <c r="T6" s="26">
-        <v>900</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
-        <v>45416</v>
-      </c>
-      <c r="B7" s="13">
-        <v>45430</v>
-      </c>
-      <c r="C7" s="13">
-        <v>45432</v>
-      </c>
-      <c r="D7" s="1">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>3</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S7" s="13">
-        <v>45416</v>
-      </c>
-      <c r="T7" s="26">
-        <v>18650</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
-        <v>45417</v>
-      </c>
-      <c r="B8" s="13">
-        <v>45432</v>
-      </c>
-      <c r="C8" s="13">
-        <v>45434</v>
-      </c>
-      <c r="D8" s="1">
-        <v>21</v>
-      </c>
-      <c r="E8" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S8" s="13">
-        <v>45417</v>
-      </c>
-      <c r="T8" s="26">
-        <v>5210</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
-        <v>45418</v>
-      </c>
-      <c r="B9" s="13">
-        <v>45437</v>
-      </c>
-      <c r="C9" s="13">
-        <v>45440</v>
-      </c>
-      <c r="D9" s="1">
-        <v>21</v>
-      </c>
-      <c r="E9" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S9" s="13">
-        <v>45418</v>
-      </c>
-      <c r="T9" s="26">
-        <v>16240</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
-        <v>45419</v>
-      </c>
-      <c r="B10" s="13">
-        <v>45439</v>
-      </c>
-      <c r="C10" s="13">
-        <v>45439</v>
-      </c>
-      <c r="D10" s="1">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="S10" s="13">
-        <v>45419</v>
-      </c>
-      <c r="T10" s="26">
-        <v>750</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
-        <v>45420</v>
-      </c>
-      <c r="B11" s="13">
-        <v>45442</v>
-      </c>
-      <c r="C11" s="13">
-        <v>45443</v>
-      </c>
-      <c r="D11" s="1">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1">
-        <f>Table1[[#This Row],[Date Of Return]]-Table1[[#This Row],[Date Of Departure]]+1</f>
-        <v>2</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="S11" s="13">
-        <v>45420</v>
-      </c>
-      <c r="T11" s="26">
-        <v>2950</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>69</v>
-      </c>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3125,15 +2285,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="649e210f-8831-4297-886a-e2be1dbb4894" xsi:nil="true"/>
@@ -3153,14 +2304,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A9DE9C-585E-451C-8169-7F73010FDB41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A9DE9C-585E-451C-8169-7F73010FDB41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0a1e28df-cf30-4b9c-bfdf-d691394ac018"/>
+    <ds:schemaRef ds:uri="649e210f-8831-4297-886a-e2be1dbb4894"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76DE3F1A-8259-4276-B004-B9EE7C10D5BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0390BCE-9210-4185-97A4-CCA2F5888C27}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="649e210f-8831-4297-886a-e2be1dbb4894"/>
+    <ds:schemaRef ds:uri="0a1e28df-cf30-4b9c-bfdf-d691394ac018"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0390BCE-9210-4185-97A4-CCA2F5888C27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76DE3F1A-8259-4276-B004-B9EE7C10D5BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>